--- a/Trip_Data_Store/uhc_full_data_sample.xlsx
+++ b/Trip_Data_Store/uhc_full_data_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kshema/python/Four-Line-Travels/Trip_Data_Store/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3E44FAA-3D07-DD48-B56F-C3185A3FDD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D46B89-2D0B-3E43-9F1A-3025CE9632B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{5CFEB719-990A-1048-97CB-87C707300CFD}"/>
+    <workbookView xWindow="6160" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{5CFEB719-990A-1048-97CB-87C707300CFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>Facility Name</t>
   </si>
   <si>
-    <t>Patient Address</t>
-  </si>
-  <si>
     <t>John Smith</t>
   </si>
   <si>
@@ -122,7 +119,10 @@
     <t>Emerson Health and Rehabilitation Center</t>
   </si>
   <si>
-    <t>100 Kinderkamack Rd, Emerson, NJ 07630</t>
+    <t>Destination Address</t>
+  </si>
+  <si>
+    <t>132 second st, Mhwah NJ 07430</t>
   </si>
 </sst>
 </file>
@@ -512,6 +512,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF25B4B6-6C6F-5948-B6FF-F91FEE7A29CE}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="50.33203125" customWidth="1"/>
+    <col min="7" max="7" width="57.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -533,122 +537,122 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>123456789</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3">
         <v>46084</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="2">
         <v>987654321</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="3">
         <v>46085</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C4" s="2">
         <v>555666777</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3">
         <v>46086</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C5" s="2">
         <v>444555666</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3">
         <v>46087</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C6" s="2">
         <v>333444555</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3">
         <v>46088</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
